--- a/docs/literature.xlsx
+++ b/docs/literature.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AdikariAdikari\PycharmProjects\ST-GNN\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37494DFD-E938-45B3-9D12-3AE1D6792848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969C307B-CDDD-4E2A-81BC-D5497D277CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51720" yWindow="10470" windowWidth="29040" windowHeight="15720" xr2:uid="{32E5EEDB-591B-4588-9B60-A382D767E49A}"/>
+    <workbookView xWindow="-60120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{32E5EEDB-591B-4588-9B60-A382D767E49A}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="581">
   <si>
     <t>Year</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>Type II</t>
-  </si>
-  <si>
-    <t>Type III</t>
   </si>
   <si>
     <t>Feature</t>
@@ -348,9 +345,6 @@
   </si>
   <si>
     <t>Physical Law/ Constraint</t>
-  </si>
-  <si>
-    <t>No Constraint</t>
   </si>
   <si>
     <t>Dynamically build edges based on the attention modules</t>
@@ -610,11 +604,6 @@
 Mean sea level pressure</t>
   </si>
   <si>
-    <t>MAE, MSE, R2, 
-Pearson correlation
- coefficient</t>
-  </si>
-  <si>
     <t>65 years</t>
   </si>
   <si>
@@ -956,13 +945,6 @@
 structural prior. Connectivity is determined by 
 geographic adjacency — an external physical 
 fact — not by training.</t>
-  </si>
-  <si>
-    <t>Explicitly flagged as "No Constraint" in the extraction. 
-The random drop mechanism is a regularisation 
-technique with no physical motivation. This is the 
-weakest form of graph construction in the corpus —
- purely data-driven with deliberate stochasticity.</t>
   </si>
   <si>
     <t>The graph encodes physical geography (station 
@@ -1060,34 +1042,6 @@
 dai2025 and chen2023.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Despite being listed under "Dynamic Constraint", the 
-described mechanism — constructing a knowledge
-graph from geographic and hydrological data — is a 
-physics-informed structural encoding. The knowledge 
-graph relationships are defined by domain knowledge 
-(physical geography, hydrological connectivity), not
-learned from data statistics. The use of "knowledge 
-graph" implies predefined, semantically grounded 
-edges. This is closer to a Type II hard constraint than
-a learned adjacency. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Note: this classification should 
-be verified against the full paper — if the knowledge 
-graph edges are updated by attention during training, 
-the classification shifts to Hybrid.</t>
-    </r>
-  </si>
-  <si>
     <t>A predefined adjacency matrix is the canonical 
 example of a hard architectural constraint. The matrix
  is fixed before training based on physical and 
@@ -1099,79 +1053,6 @@
  physical flow causality. This is a directional physical
  constraint embedded in the graph topology by 
 construction, identical in principle to akkala2025.</t>
-  </si>
-  <si>
-    <t>Dynamic graph 
-(physics-driven)</t>
-  </si>
-  <si>
-    <t>Dynamic graph 
-(vision-driven)</t>
-  </si>
-  <si>
-    <t>Where physics enters</t>
-  </si>
-  <si>
-    <t>Constraint strength</t>
-  </si>
-  <si>
-    <t>Example in hydrology GNNs</t>
-  </si>
-  <si>
-    <t>Loss function penalty term</t>
-  </si>
-  <si>
-    <t>Architecture by construction</t>
-  </si>
-  <si>
-    <t>Hard at topology level</t>
-  </si>
-  <si>
-    <t>Soft — can be violated</t>
-  </si>
-  <si>
-    <t>Hard — cannot be violated</t>
-  </si>
-  <si>
-    <t>Input features from physics
- model</t>
-  </si>
-  <si>
-    <t>Edge weights recomputed 
-from equations</t>
-  </si>
-  <si>
-    <t>Edge attributes from CV 
-outputs</t>
-  </si>
-  <si>
-    <t>Indirect — inherited from
-model</t>
-  </si>
-  <si>
-    <t>Soft-to-hard depending on 
-mapping</t>
-  </si>
-  <si>
-    <t>Mass conservation residual 
-at junctions</t>
-  </si>
-  <si>
-    <t>Non-negative discharge 
-output; monotonic rating curves</t>
-  </si>
-  <si>
-    <t>HBV / VIC outputs as node
- features</t>
-  </si>
-  <si>
-    <t>Manning-derived travel times 
-as time-varying edge weights</t>
-  </si>
-  <si>
-    <t>Debris density → 
-Manning's nn n →
- flow resistance factor</t>
   </si>
   <si>
     <t>Transformer Encoder +
@@ -1637,10 +1518,6 @@
 physics-based connectivity of the vector hydrograph</t>
   </si>
   <si>
-    <t>Upstream/Downstream
- Identifiers/connections</t>
-  </si>
-  <si>
     <t>Reach identification
 number (COMID)</t>
   </si>
@@ -1706,10 +1583,6 @@
   </si>
   <si>
     <t>HydroGraphNet</t>
-  </si>
-  <si>
-    <t>RMSE, NSE, CSI (Critical 
-success index)</t>
   </si>
   <si>
     <t>Water depth prediction</t>
@@ -1921,9 +1794,6 @@
     <t>Discharge, Rainfall</t>
   </si>
   <si>
-    <t>RMSE, DC</t>
-  </si>
-  <si>
     <t>Predict the river discharge</t>
   </si>
   <si>
@@ -2014,9 +1884,6 @@
     <t>bentivoglioMultiscaleHydraulicGraph2025a</t>
   </si>
   <si>
-    <t>MAE, CSI</t>
-  </si>
-  <si>
     <t>mSWE-GNN</t>
   </si>
   <si>
@@ -2068,10 +1935,6 @@
   </si>
   <si>
     <t>FloodGNN-GRU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMSE, NSE, CSI,
-Pearson correlation </t>
   </si>
   <si>
     <t>6 days (Event specific)</t>
@@ -2224,9 +2087,6 @@
 both temporal and spatial patterns</t>
   </si>
   <si>
-    <t>Learned-dynamic</t>
-  </si>
-  <si>
     <t>Dynamically build adjucency matrix based on the attention modules</t>
   </si>
   <si>
@@ -2313,13 +2173,43 @@
   </si>
   <si>
     <t>SAR, LiDAR-derived DEM</t>
+  </si>
+  <si>
+    <t>RMSE, DC, FPE</t>
+  </si>
+  <si>
+    <t>MAE, MSE, R2, 
+CORR</t>
+  </si>
+  <si>
+    <t>RMSE, NSE, CSI,
+CORR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upstream/Downstream </t>
+  </si>
+  <si>
+    <t>MAE, CSI, FAT</t>
+  </si>
+  <si>
+    <t>RMSE, NSE, CSI (Critical 
+success index), FAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Learned-Dynamic</t>
+  </si>
+  <si>
+    <t>During knowledge graph construction, various sites, rivers, and administrative regions were defined as nodes, while relationships, such as the river to which a site belongs and the administrative region in which it is located, were represented as edges between these nodes. The knowledge graph was constructed and maintained using Neo4j. The final knowledge graph consists of 180 nodes and 220 edges. Each node in the knowledge graph represents not merely a point, but an entity enriched with contextual knowledge, capturing river connectivity and regional affiliation between sites, which allow the model to more effectively learn the spatial dependencies and influence pathways between hydrological stations.</t>
+  </si>
+  <si>
+    <t>Generally, the river network can be regarded as a network of graph structure in essence. All cities and hydrological survey points on the river network can be regarded as nodes, and the characteristics of each node can be regarded as signals on the graph. Therefore, In order to extract topological features of river networks more fully, we combine the constructed hydrographic graph with spatial-temporal attention mechanism to conduct graph convolution operation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2329,14 +2219,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -2424,7 +2306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2476,6 +2358,9 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2818,7 +2703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158418F5-96F6-4AEF-AF09-273EC1E50873}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="48.62890625" customWidth="1"/>
@@ -2854,1231 +2739,1234 @@
         <v>13</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="14">
         <v>2025</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>601</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>31</v>
-      </c>
       <c r="J2" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="6">
         <v>2025</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="10">
         <v>2025</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B5" s="6">
         <v>2023</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="G5" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B6" s="6">
         <v>2023</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B7" s="6">
         <v>2022</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B8" s="6">
         <v>2021</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B9" s="6">
         <v>2025</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="J9" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B10" s="10">
         <v>2025</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B11" s="10">
         <v>2025</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B12" s="8">
         <v>2025</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>201</v>
-      </c>
       <c r="J12" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B13" s="6">
         <v>2025</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>215</v>
-      </c>
       <c r="J13" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B14" s="6">
         <v>2024</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B15" s="10">
         <v>2026</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B16" s="8">
         <v>2025</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>242</v>
-      </c>
       <c r="I16" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B17" s="8">
         <v>2025</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="10" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="B18" s="10">
         <v>2024</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="8" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B19" s="8">
         <v>2023</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="B20" s="6">
         <v>2026</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="B21" s="6">
         <v>2026</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="16" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="B22" s="16">
         <v>2025</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="8" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="B23" s="8">
         <v>2023</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="8" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="B24" s="8">
         <v>2025</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>602</v>
+        <v>571</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="6" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="B25" s="6">
         <v>2023</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="B26" s="8">
         <v>2022</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="12" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="12" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="B27" s="12">
         <v>2024</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="10" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="B28" s="10">
         <v>2025</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>438</v>
+        <v>577</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="B29" s="6">
         <v>2025</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="B30" s="8">
         <v>2025</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="B31" s="8">
         <v>2026</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="B32" s="8">
         <v>2020</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>494</v>
+        <v>572</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>495</v>
+        <v>467</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="8" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="B33" s="8">
         <v>2023</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>504</v>
+        <v>476</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="16" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="B34" s="16">
         <v>2023</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>514</v>
+        <v>486</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>513</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="16" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="B35" s="16">
         <v>2025</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>520</v>
+        <v>576</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="6" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
       <c r="B36" s="6">
         <v>2024</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="8" t="s">
-        <v>545</v>
+        <v>515</v>
       </c>
       <c r="B37" s="8">
         <v>2025</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="I37" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>31</v>
-      </c>
       <c r="J37" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="8" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
       <c r="B38" s="8">
         <v>2026</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>552</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="8" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="B39" s="8">
         <v>2024</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>320</v>
-      </c>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="G45" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4125,10 +4013,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>14</v>
@@ -4136,960 +4024,960 @@
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="H3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" t="s">
         <v>86</v>
       </c>
-      <c r="G4" t="s">
-        <v>87</v>
-      </c>
       <c r="H4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="G6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="I6" s="26"/>
+      <c r="I6" s="27"/>
       <c r="J6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="C7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>182</v>
-      </c>
       <c r="J10" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="J13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="G14" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:95 1836:1836" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I17" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:95 1836:1836" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="B18" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="J18" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:95 1836:1836" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="J19" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:95 1836:1836" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:95 1836:1836" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="B21" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:95 1836:1836" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="B22" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="J22" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:95 1836:1836" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="B23" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="J23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:95 1836:1836" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="B24" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="J24" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:95 1836:1836" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:95 1836:1836" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
     </row>
     <row r="27" spans="1:95 1836:1836" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:95 1836:1836" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="B28" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="G28" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:95 1836:1836" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="J29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:95 1836:1836" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:95 1836:1836" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="E31" s="5" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CQ31" s="4">
         <v>0</v>
@@ -5097,37 +4985,37 @@
     </row>
     <row r="32" spans="1:95 1836:1836" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>497</v>
+        <v>469</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>496</v>
+        <v>468</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CQ32" s="4" t="s">
-        <v>319</v>
+        <v>294</v>
       </c>
       <c r="BRP32" s="4">
         <v>0</v>
@@ -5135,34 +5023,34 @@
     </row>
     <row r="33" spans="1:10 1836:1836" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="B33" t="s">
-        <v>505</v>
+        <v>477</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>506</v>
+        <v>478</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>507</v>
+        <v>479</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BRP33">
         <v>8.8999999999999996E-2</v>
@@ -5170,194 +5058,194 @@
     </row>
     <row r="34" spans="1:10 1836:1836" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="B34" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>526</v>
+        <v>497</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="J34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:10 1836:1836" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="B35" t="s">
-        <v>521</v>
+        <v>492</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>527</v>
+        <v>498</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J35" t="s">
-        <v>529</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:10 1836:1836" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
       <c r="B36" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>497</v>
+        <v>469</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>541</v>
+        <v>511</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>537</v>
+        <v>507</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>538</v>
+        <v>508</v>
       </c>
       <c r="J36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:10 1836:1836" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4" t="s">
-        <v>545</v>
+        <v>515</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>546</v>
+        <v>516</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="I37" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:10 1836:1836" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>553</v>
+        <v>523</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>555</v>
+        <v>525</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:10 1836:1836" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="B39" t="s">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>561</v>
+        <v>531</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J39" t="s">
-        <v>563</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -5395,13 +5283,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -5409,13 +5297,13 @@
     </row>
     <row r="3" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="D3" s="16">
         <v>54</v>
@@ -5423,13 +5311,13 @@
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4">
         <v>31</v>
@@ -5437,13 +5325,13 @@
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -5451,13 +5339,13 @@
     </row>
     <row r="6" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" s="16">
         <v>5</v>
@@ -5465,69 +5353,69 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D11">
         <v>534</v>
@@ -5535,13 +5423,13 @@
     </row>
     <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -5549,13 +5437,13 @@
     </row>
     <row r="13" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="D13" s="18">
         <v>62498</v>
@@ -5563,41 +5451,41 @@
     </row>
     <row r="14" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -5605,13 +5493,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C17" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="D17">
         <v>45</v>
@@ -5619,13 +5507,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="B18" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="D18">
         <v>9</v>
@@ -5633,13 +5521,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B19" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="D19">
         <v>26</v>
@@ -5647,13 +5535,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="D20" s="3">
         <v>9</v>
@@ -5661,13 +5549,13 @@
     </row>
     <row r="21" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="16" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="B21" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="D21" s="16">
         <v>1435271</v>
@@ -5675,13 +5563,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="B22" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="C22" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="D22">
         <v>48</v>
@@ -5689,13 +5577,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="D23">
         <v>186</v>
@@ -5703,13 +5591,13 @@
     </row>
     <row r="24" spans="1:4" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="16" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="D24" s="16">
         <v>2226</v>
@@ -5717,13 +5605,13 @@
     </row>
     <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="D25">
         <v>7</v>
@@ -5731,13 +5619,13 @@
     </row>
     <row r="26" spans="1:4" s="10" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="10" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="D26" s="10">
         <v>1708</v>
@@ -5745,13 +5633,13 @@
     </row>
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="D27">
         <v>219</v>
@@ -5759,13 +5647,13 @@
     </row>
     <row r="28" spans="1:4" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="16" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="D28" s="16">
         <v>4787</v>
@@ -5773,13 +5661,13 @@
     </row>
     <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="D29">
         <v>358</v>
@@ -5787,13 +5675,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="D30">
         <v>11</v>
@@ -5801,13 +5689,13 @@
     </row>
     <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="D31">
         <v>16</v>
@@ -5815,13 +5703,13 @@
     </row>
     <row r="32" spans="1:4" s="24" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="24" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="D32" s="24">
         <v>139</v>
@@ -5829,13 +5717,13 @@
     </row>
     <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>508</v>
+        <v>480</v>
       </c>
       <c r="D33">
         <v>77</v>
@@ -5843,13 +5731,13 @@
     </row>
     <row r="34" spans="1:4" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="16" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="D34" s="16">
         <v>16384</v>
@@ -5857,13 +5745,13 @@
     </row>
     <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="B35" t="s">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="D35">
         <v>22881</v>
@@ -5871,13 +5759,13 @@
     </row>
     <row r="36" spans="1:4" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="16" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>542</v>
+        <v>512</v>
       </c>
       <c r="D36" s="18">
         <v>3208196</v>
@@ -5885,13 +5773,13 @@
     </row>
     <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>545</v>
+        <v>515</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>548</v>
+        <v>518</v>
       </c>
       <c r="D37">
         <v>20</v>
@@ -5899,13 +5787,13 @@
     </row>
     <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>548</v>
+        <v>518</v>
       </c>
       <c r="D38">
         <v>235</v>
@@ -5913,13 +5801,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="B39" t="s">
-        <v>563</v>
+        <v>533</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="D39">
         <v>544</v>
@@ -5953,7 +5841,7 @@
         <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -5962,362 +5850,306 @@
         <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>278</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="16" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>289</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" s="19" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>290</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="I3" s="20"/>
     </row>
     <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>579</v>
+        <v>549</v>
       </c>
       <c r="D4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>291</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>581</v>
+        <v>550</v>
       </c>
       <c r="D5" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>292</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" s="19" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>259</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="1:9" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>583</v>
+        <v>552</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>263</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>583</v>
+        <v>552</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D9" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="19" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="19" customFormat="1" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="19" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="19" customFormat="1" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="19" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>585</v>
+        <v>554</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="19" customFormat="1" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="19" customFormat="1" ht="201.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>227</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>230</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>271</v>
+        <v>579</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="19" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>19</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="19" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="19" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>19</v>
@@ -6325,42 +6157,42 @@
     </row>
     <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" s="22" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="22" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="19" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>354</v>
+        <v>329</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>19</v>
@@ -6368,13 +6200,13 @@
     </row>
     <row r="22" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="19" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>19</v>
@@ -6382,69 +6214,69 @@
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="D23" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="19" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="19" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>591</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>592</v>
+        <v>561</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>593</v>
+        <v>562</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="19" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>19</v>
@@ -6452,13 +6284,13 @@
     </row>
     <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -6466,13 +6298,13 @@
     </row>
     <row r="29" spans="1:5" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="19" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>19</v>
@@ -6480,69 +6312,69 @@
     </row>
     <row r="30" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>594</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>595</v>
+        <v>564</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>500</v>
+        <v>472</v>
       </c>
       <c r="D32" t="s">
-        <v>596</v>
+        <v>565</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>509</v>
+        <v>481</v>
       </c>
       <c r="D33" t="s">
-        <v>597</v>
+        <v>566</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>518</v>
+        <v>490</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -6550,13 +6382,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
@@ -6564,13 +6396,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>543</v>
+        <v>513</v>
       </c>
       <c r="D36" t="s">
         <v>19</v>
@@ -6578,13 +6410,13 @@
     </row>
     <row r="37" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="19" t="s">
-        <v>545</v>
+        <v>515</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>19</v>
@@ -6592,30 +6424,30 @@
     </row>
     <row r="38" spans="1:4" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="19" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="19" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -6635,21 +6467,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -6657,10 +6489,10 @@
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6668,10 +6500,10 @@
     </row>
     <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6679,10 +6511,10 @@
     </row>
     <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6690,10 +6522,10 @@
     </row>
     <row r="6" spans="1:3" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>62</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -6701,19 +6533,19 @@
     </row>
     <row r="7" spans="1:3" ht="47.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="28"/>
+        <v>61</v>
+      </c>
+      <c r="B7" s="29"/>
       <c r="C7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6721,10 +6553,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -6732,10 +6564,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -6743,10 +6575,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6754,10 +6586,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6765,7 +6597,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -6773,7 +6605,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -6781,7 +6613,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -6789,7 +6621,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -6797,7 +6629,7 @@
     </row>
     <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -6805,7 +6637,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C18">
         <v>9</v>
@@ -6813,21 +6645,21 @@
     </row>
     <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
-        <v>418</v>
+        <v>575</v>
       </c>
       <c r="B20" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -6835,10 +6667,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="B21" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -6846,10 +6678,10 @@
     </row>
     <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -6857,10 +6689,10 @@
     </row>
     <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -6868,7 +6700,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -6876,7 +6708,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -6884,7 +6716,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -6892,7 +6724,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -6900,7 +6732,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -6908,7 +6740,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -6916,7 +6748,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -6924,7 +6756,7 @@
     </row>
     <row r="31" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -6932,7 +6764,7 @@
     </row>
     <row r="32" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6945,7 +6777,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6953,7 +6785,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -6961,7 +6793,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -6969,7 +6801,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>467</v>
+        <v>440</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6977,7 +6809,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>468</v>
+        <v>441</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6985,7 +6817,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>469</v>
+        <v>442</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -6993,7 +6825,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -7001,7 +6833,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
-        <v>471</v>
+        <v>444</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -7009,7 +6841,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -7017,7 +6849,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -7025,7 +6857,7 @@
     </row>
     <row r="44" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -7033,7 +6865,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>569</v>
+        <v>539</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -7041,7 +6873,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>572</v>
+        <v>542</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -7049,7 +6881,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -7057,7 +6889,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -7065,7 +6897,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -7073,7 +6905,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50">
@@ -7082,7 +6914,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>575</v>
+        <v>545</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -7090,7 +6922,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -7098,7 +6930,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>577</v>
+        <v>547</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -7106,7 +6938,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>578</v>
+        <v>548</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -7136,18 +6968,18 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>17</v>
@@ -7155,7 +6987,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -7163,7 +6995,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="C4">
         <v>23</v>
@@ -7171,7 +7003,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -7179,7 +7011,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -7187,7 +7019,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7195,7 +7027,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -7203,7 +7035,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -7211,7 +7043,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -7219,7 +7051,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -7227,7 +7059,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -7235,7 +7067,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -7243,7 +7075,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -7251,10 +7083,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -7263,10 +7095,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -7274,10 +7106,10 @@
     </row>
     <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -7285,10 +7117,10 @@
     </row>
     <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -7296,10 +7128,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -7307,10 +7139,10 @@
     </row>
     <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -7318,7 +7150,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -7326,7 +7158,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -7334,7 +7166,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -7342,7 +7174,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -7350,7 +7182,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -7358,7 +7190,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -7366,7 +7198,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -7374,7 +7206,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -7382,7 +7214,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -7390,7 +7222,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -7398,7 +7230,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -7406,7 +7238,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -7414,7 +7246,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -7422,7 +7254,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
-        <v>566</v>
+        <v>536</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -7430,7 +7262,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
-        <v>567</v>
+        <v>537</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -7438,7 +7270,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
-        <v>568</v>
+        <v>538</v>
       </c>
       <c r="C36">
         <v>1</v>

--- a/docs/literature.xlsx
+++ b/docs/literature.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AdikariAdikari\PycharmProjects\ST-GNN\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969C307B-CDDD-4E2A-81BC-D5497D277CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3D5EF8-385F-42A1-AE1A-C2A68FFF8D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{32E5EEDB-591B-4588-9B60-A382D767E49A}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="37920" activeTab="1" xr2:uid="{32E5EEDB-591B-4588-9B60-A382D767E49A}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="582">
   <si>
     <t>Year</t>
   </si>
@@ -101,9 +101,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Type I</t>
   </si>
   <si>
     <t>Type II</t>
@@ -2203,6 +2200,16 @@
   </si>
   <si>
     <t>Generally, the river network can be regarded as a network of graph structure in essence. All cities and hydrological survey points on the river network can be regarded as nodes, and the characteristics of each node can be regarded as signals on the graph. Therefore, In order to extract topological features of river networks more fully, we combine the constructed hydrographic graph with spatial-temporal attention mechanism to conduct graph convolution operation</t>
+  </si>
+  <si>
+    <t>Type I + Type II</t>
+  </si>
+  <si>
+    <t>The floodplain is represented as a computational 
+mesh graph (nodes = mesh points, 
+edges = neighboring-node adjacency) ; 
+a hard structural prior with the residual physics 
+penalty (Type I) applied on top during training</t>
   </si>
 </sst>
 </file>
@@ -2739,1230 +2746,1230 @@
         <v>13</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="14">
         <v>2025</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>570</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>30</v>
-      </c>
       <c r="J2" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="6">
         <v>2025</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="10">
         <v>2025</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" s="6">
         <v>2023</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="6">
         <v>2023</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B7" s="6">
         <v>2022</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B8" s="6">
         <v>2021</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B9" s="6">
         <v>2025</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" s="10">
         <v>2025</v>
       </c>
       <c r="C10" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" s="10">
         <v>2025</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B12" s="8">
         <v>2025</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B13" s="6">
         <v>2025</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>209</v>
-      </c>
       <c r="G13" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14" s="6">
         <v>2024</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>218</v>
-      </c>
       <c r="J14" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B15" s="10">
         <v>2026</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B16" s="8">
         <v>2025</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>236</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B17" s="8">
         <v>2025</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B18" s="10">
         <v>2024</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B19" s="8">
         <v>2023</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B20" s="6">
         <v>2026</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="G20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>314</v>
-      </c>
       <c r="J20" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B21" s="6">
         <v>2026</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H21" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>327</v>
-      </c>
       <c r="J21" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B22" s="16">
         <v>2025</v>
       </c>
       <c r="C22" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="J22" s="17" t="s">
         <v>335</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B23" s="8">
         <v>2023</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B24" s="8">
         <v>2025</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B25" s="6">
         <v>2023</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B26" s="8">
         <v>2022</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="12" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B27" s="12">
         <v>2024</v>
       </c>
       <c r="C27" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="J27" s="13" t="s">
         <v>398</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B28" s="10">
         <v>2025</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B29" s="6">
         <v>2025</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B30" s="8">
         <v>2025</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B31" s="8">
         <v>2026</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F31" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>458</v>
-      </c>
       <c r="J31" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B32" s="8">
         <v>2020</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B33" s="8">
         <v>2023</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F33" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>476</v>
-      </c>
       <c r="J33" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="16" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B34" s="16">
         <v>2023</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="16" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B35" s="16">
         <v>2025</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I35" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="J35" s="17" t="s">
         <v>493</v>
-      </c>
-      <c r="J35" s="17" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B36" s="6">
         <v>2024</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B37" s="8">
         <v>2025</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="I37" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="J37" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B38" s="8">
         <v>2026</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B39" s="8">
         <v>2024</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4013,10 +4020,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>14</v>
@@ -4024,960 +4031,960 @@
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="H3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" t="s">
         <v>85</v>
       </c>
-      <c r="G4" t="s">
-        <v>86</v>
-      </c>
       <c r="H4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="J4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I6" s="27"/>
       <c r="J6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" t="s">
         <v>145</v>
       </c>
-      <c r="I7" t="s">
-        <v>146</v>
-      </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="J10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="C14" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>221</v>
-      </c>
       <c r="J14" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>234</v>
-      </c>
       <c r="C16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:95 1836:1836" s="4" customFormat="1" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="J17" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:95 1836:1836" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="J18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:95 1836:1836" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
+        <v>295</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="C19" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="G19" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="J19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:95 1836:1836" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="I20" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:95 1836:1836" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>322</v>
+      </c>
+      <c r="B21" t="s">
         <v>323</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:95 1836:1836" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="I22" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J22" t="s">
         <v>344</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="J22" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:95 1836:1836" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B23" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="J23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:95 1836:1836" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" t="s">
         <v>361</v>
       </c>
-      <c r="B24" t="s">
-        <v>362</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="I24" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="J24" t="s">
         <v>368</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="J24" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:95 1836:1836" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
+        <v>372</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>374</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>379</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:95 1836:1836" s="4" customFormat="1" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="G26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="27" spans="1:95 1836:1836" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>406</v>
-      </c>
       <c r="J27" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:95 1836:1836" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
+        <v>409</v>
+      </c>
+      <c r="B28" t="s">
         <v>410</v>
       </c>
-      <c r="B28" t="s">
-        <v>411</v>
-      </c>
       <c r="C28" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G28" t="s">
         <v>415</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="H28" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>418</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" spans="1:95 1836:1836" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="E29" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>435</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:95 1836:1836" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>448</v>
-      </c>
       <c r="C30" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:95 1836:1836" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="E31" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>460</v>
-      </c>
       <c r="G31" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CQ31" s="4">
         <v>0</v>
@@ -4985,37 +4992,37 @@
     </row>
     <row r="32" spans="1:95 1836:1836" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E32" s="5" t="s">
+      <c r="G32" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>471</v>
-      </c>
       <c r="I32" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CQ32" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BRP32" s="4">
         <v>0</v>
@@ -5023,34 +5030,34 @@
     </row>
     <row r="33" spans="1:10 1836:1836" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B33" t="s">
+        <v>476</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BRP33">
         <v>8.8999999999999996E-2</v>
@@ -5058,194 +5065,194 @@
     </row>
     <row r="34" spans="1:10 1836:1836" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
+        <v>482</v>
+      </c>
+      <c r="B34" t="s">
         <v>483</v>
       </c>
-      <c r="B34" t="s">
-        <v>484</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="J34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:10 1836:1836" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
+        <v>490</v>
+      </c>
+      <c r="B35" t="s">
         <v>491</v>
       </c>
-      <c r="B35" t="s">
-        <v>492</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E35" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="I35" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J35" t="s">
         <v>499</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="J35" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:10 1836:1836" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
+        <v>503</v>
+      </c>
+      <c r="B36" t="s">
         <v>504</v>
       </c>
-      <c r="B36" t="s">
-        <v>505</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E36" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="H36" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="J36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:10 1836:1836" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>516</v>
-      </c>
       <c r="C37" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="I37" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:10 1836:1836" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:10 1836:1836" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
+        <v>526</v>
+      </c>
+      <c r="B39" t="s">
         <v>527</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="G39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="I39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J39" t="s">
         <v>532</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J39" t="s">
-        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -5283,13 +5290,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D2">
         <v>20</v>
@@ -5297,13 +5304,13 @@
     </row>
     <row r="3" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="D3" s="16">
         <v>54</v>
@@ -5311,13 +5318,13 @@
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D4">
         <v>31</v>
@@ -5325,13 +5332,13 @@
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -5339,13 +5346,13 @@
     </row>
     <row r="6" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="16">
         <v>5</v>
@@ -5353,69 +5360,69 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D11">
         <v>534</v>
@@ -5423,13 +5430,13 @@
     </row>
     <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -5437,13 +5444,13 @@
     </row>
     <row r="13" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="D13" s="18">
         <v>62498</v>
@@ -5451,41 +5458,41 @@
     </row>
     <row r="14" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -5493,13 +5500,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D17">
         <v>45</v>
@@ -5507,13 +5514,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B18" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D18">
         <v>9</v>
@@ -5521,13 +5528,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D19">
         <v>26</v>
@@ -5535,13 +5542,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D20" s="3">
         <v>9</v>
@@ -5549,13 +5556,13 @@
     </row>
     <row r="21" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>67</v>
       </c>
       <c r="D21" s="16">
         <v>1435271</v>
@@ -5563,13 +5570,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C22" t="s">
         <v>345</v>
-      </c>
-      <c r="C22" t="s">
-        <v>346</v>
       </c>
       <c r="D22">
         <v>48</v>
@@ -5577,13 +5584,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D23">
         <v>186</v>
@@ -5591,13 +5598,13 @@
     </row>
     <row r="24" spans="1:4" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B24" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>369</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>370</v>
       </c>
       <c r="D24" s="16">
         <v>2226</v>
@@ -5605,13 +5612,13 @@
     </row>
     <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D25">
         <v>7</v>
@@ -5619,13 +5626,13 @@
     </row>
     <row r="26" spans="1:4" s="10" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>390</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>391</v>
       </c>
       <c r="D26" s="10">
         <v>1708</v>
@@ -5633,13 +5640,13 @@
     </row>
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D27">
         <v>219</v>
@@ -5647,13 +5654,13 @@
     </row>
     <row r="28" spans="1:4" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="16" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D28" s="16">
         <v>4787</v>
@@ -5661,13 +5668,13 @@
     </row>
     <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D29">
         <v>358</v>
@@ -5675,13 +5682,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D30">
         <v>11</v>
@@ -5689,13 +5696,13 @@
     </row>
     <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D31">
         <v>16</v>
@@ -5703,13 +5710,13 @@
     </row>
     <row r="32" spans="1:4" s="24" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="24" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D32" s="24">
         <v>139</v>
@@ -5717,13 +5724,13 @@
     </row>
     <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D33">
         <v>77</v>
@@ -5731,13 +5738,13 @@
     </row>
     <row r="34" spans="1:4" s="16" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="16" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D34" s="16">
         <v>16384</v>
@@ -5745,13 +5752,13 @@
     </row>
     <row r="35" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B35" t="s">
+        <v>499</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>501</v>
       </c>
       <c r="D35">
         <v>22881</v>
@@ -5759,13 +5766,13 @@
     </row>
     <row r="36" spans="1:4" s="16" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="16" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D36" s="18">
         <v>3208196</v>
@@ -5773,13 +5780,13 @@
     </row>
     <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D37">
         <v>20</v>
@@ -5787,13 +5794,13 @@
     </row>
     <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D38">
         <v>235</v>
@@ -5801,13 +5808,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B39" t="s">
+        <v>532</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="D39">
         <v>544</v>
@@ -5841,7 +5848,7 @@
         <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -5850,7 +5857,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -5859,55 +5866,55 @@
     </row>
     <row r="2" spans="1:9" s="16" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" s="19" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I3" s="20"/>
     </row>
     <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -5915,19 +5922,19 @@
     </row>
     <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -5935,19 +5942,19 @@
     </row>
     <row r="6" spans="1:9" s="19" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
@@ -5956,501 +5963,505 @@
     </row>
     <row r="7" spans="1:9" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>552</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="19" customFormat="1" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="19" customFormat="1" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="19" customFormat="1" ht="201.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="19" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" s="22" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="19" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="19" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>580</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="19" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D32" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D33" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="19" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="19" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="19" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="D1:D39" xr:uid="{701219C6-9FE2-4ADC-8AF4-C754B3EE7C82}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6467,21 +6478,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -6489,10 +6500,10 @@
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6500,10 +6511,10 @@
     </row>
     <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6511,10 +6522,10 @@
     </row>
     <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6522,10 +6533,10 @@
     </row>
     <row r="6" spans="1:3" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -6533,7 +6544,7 @@
     </row>
     <row r="7" spans="1:3" ht="47.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7">
@@ -6542,10 +6553,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s">
         <v>109</v>
-      </c>
-      <c r="B8" t="s">
-        <v>110</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6553,10 +6564,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -6564,10 +6575,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" t="s">
         <v>113</v>
-      </c>
-      <c r="B10" t="s">
-        <v>114</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -6575,10 +6586,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" t="s">
         <v>117</v>
-      </c>
-      <c r="B11" t="s">
-        <v>118</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6586,10 +6597,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" t="s">
         <v>115</v>
-      </c>
-      <c r="B12" t="s">
-        <v>116</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6597,7 +6608,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -6605,7 +6616,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -6613,7 +6624,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -6621,7 +6632,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -6629,7 +6640,7 @@
     </row>
     <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -6637,7 +6648,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C18">
         <v>9</v>
@@ -6645,10 +6656,10 @@
     </row>
     <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -6656,10 +6667,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -6667,10 +6678,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -6678,10 +6689,10 @@
     </row>
     <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -6689,10 +6700,10 @@
     </row>
     <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -6700,7 +6711,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -6708,7 +6719,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -6716,7 +6727,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -6724,7 +6735,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -6732,7 +6743,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -6740,7 +6751,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -6748,7 +6759,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -6756,7 +6767,7 @@
     </row>
     <row r="31" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -6764,7 +6775,7 @@
     </row>
     <row r="32" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6777,7 +6788,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6785,7 +6796,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -6793,7 +6804,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -6801,7 +6812,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6809,7 +6820,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6817,7 +6828,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -6825,7 +6836,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -6833,7 +6844,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -6841,7 +6852,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -6849,7 +6860,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -6857,7 +6868,7 @@
     </row>
     <row r="44" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6865,7 +6876,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6873,7 +6884,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6881,7 +6892,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6889,7 +6900,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6897,7 +6908,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6905,7 +6916,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50">
@@ -6914,7 +6925,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6922,7 +6933,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6930,7 +6941,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6938,7 +6949,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6968,18 +6979,18 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>17</v>
@@ -6987,7 +6998,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -6995,7 +7006,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C4">
         <v>23</v>
@@ -7003,7 +7014,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -7011,7 +7022,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -7019,7 +7030,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7027,7 +7038,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -7035,7 +7046,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -7043,7 +7054,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -7051,7 +7062,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -7059,7 +7070,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -7067,7 +7078,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -7075,7 +7086,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -7083,10 +7094,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" t="s">
         <v>119</v>
-      </c>
-      <c r="B15" t="s">
-        <v>120</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -7095,10 +7106,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" t="s">
         <v>121</v>
-      </c>
-      <c r="B16" t="s">
-        <v>122</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -7106,10 +7117,10 @@
     </row>
     <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -7117,10 +7128,10 @@
     </row>
     <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -7128,10 +7139,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" t="s">
         <v>127</v>
-      </c>
-      <c r="B19" t="s">
-        <v>128</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -7139,10 +7150,10 @@
     </row>
     <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -7150,7 +7161,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -7158,7 +7169,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -7166,7 +7177,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -7174,7 +7185,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -7182,7 +7193,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -7190,7 +7201,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -7198,7 +7209,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -7206,7 +7217,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -7214,7 +7225,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -7222,7 +7233,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -7230,7 +7241,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -7238,7 +7249,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -7246,7 +7257,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -7254,7 +7265,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -7262,7 +7273,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -7270,7 +7281,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C36">
         <v>1</v>
